--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3260-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3260-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{164ADB8F-6858-4919-B0AB-BC4C76FFB275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3F107F2-1E44-4EC9-92FB-501C9EC4685C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3BD447E5-DDD5-4E01-BE76-23BE1DC7BD2C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B8B9EE7B-A32D-47EE-BA01-998E81AAA883}"/>
   </bookViews>
   <sheets>
     <sheet name="3260-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1547,30 +1547,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1043EAE-DE5B-4BA7-A998-1215C73BD6D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965B627A-A372-47FB-A9A2-6DFC6283947A}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1760,7 +1760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2023</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2022</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2021</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2020</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2019</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2018</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2017</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2016</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2015</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2014</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="42">
         <v>2013</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="44"/>
       <c r="B27" s="45"/>
       <c r="C27" s="20" t="s">
@@ -3390,7 +3390,7 @@
       <c r="W27" s="51"/>
       <c r="X27" s="47"/>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2012</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2011</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2010</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2009</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2008</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2007</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>2006</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2005</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>2004</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2003</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>2002</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2001</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
         <v>57</v>
       </c>
